--- a/TestData/apiData.xlsx
+++ b/TestData/apiData.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="72">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="82">
   <x:si>
     <x:t>newUserBody</x:t>
   </x:si>
@@ -264,6 +264,36 @@
   </x:si>
   <x:si>
     <x:t>01kns9cpatarhffgdm3kdx028d</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dg20260410073739681@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>01kntj9ys1c1pbhj91w36j9wkq</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dg20260410075116117@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>01kntk2w0c3jk5h0hmdwfmgwtr</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dg20260410075825139@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>01kntkfz6v8z23gc7vjrqfzh1x</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dg20260410080555120@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>01kntkxpbe60w7k51bhx40jn5m</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dg20260410084521939@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>01kntp5xqy67sgc06e6xhs17c5</x:t>
   </x:si>
   <x:si>
     <x:t>token</x:t>
@@ -1092,6 +1122,61 @@
         <x:v>70</x:v>
       </x:c>
     </x:row>
+    <x:row r="41" spans="1:5">
+      <x:c r="A41" s="0" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="B41" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C41" s="0" t="s">
+        <x:v>72</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" spans="1:5">
+      <x:c r="A42" s="0" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="B42" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C42" s="0" t="s">
+        <x:v>74</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" spans="1:5">
+      <x:c r="A43" s="0" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="B43" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C43" s="0" t="s">
+        <x:v>76</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" spans="1:5">
+      <x:c r="A44" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="B44" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C44" s="0" t="s">
+        <x:v>78</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" spans="1:5">
+      <x:c r="A45" s="0" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="B45" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C45" s="0" t="s">
+        <x:v>80</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
@@ -1111,7 +1196,7 @@
   <x:sheetData>
     <x:row r="1" spans="1:17">
       <x:c r="A1" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>81</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
